--- a/data/trans_dic/P36$otros-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36$otros-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, otros alimentos</t>
+          <t>Población que desayuna, otros alimentos (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,96</t>
+          <t>1,89; 3,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,65</t>
+          <t>0,8; 2,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,87</t>
+          <t>2,38; 4,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,26</t>
+          <t>1,65; 3,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,63</t>
+          <t>0,57; 1,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,77</t>
+          <t>3,09; 5,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,32</t>
+          <t>1,98; 3,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,88</t>
+          <t>0,82; 1,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,87</t>
+          <t>3,13; 5,03</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,14</t>
+          <t>0,89; 2,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,51</t>
+          <t>0,57; 1,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 4,94</t>
+          <t>3,18; 5,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,98</t>
+          <t>0,84; 1,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,55</t>
+          <t>0,58; 1,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 4,64</t>
+          <t>2,87; 4,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,82</t>
+          <t>1,01; 1,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,34</t>
+          <t>0,65; 1,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,57</t>
+          <t>3,27; 4,54</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,49</t>
+          <t>0,48; 2,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,85</t>
+          <t>0,2; 1,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,8</t>
+          <t>3,34; 7,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,8</t>
+          <t>0,2; 1,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,04</t>
+          <t>1,02; 4,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,29</t>
+          <t>3,76; 7,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,93</t>
+          <t>0,5; 1,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,36</t>
+          <t>0,71; 2,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,88</t>
+          <t>4,03; 6,93</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,33</t>
+          <t>1,42; 2,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,49</t>
+          <t>0,72; 1,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,87</t>
+          <t>3,44; 4,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,09</t>
+          <t>1,26; 2,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,54</t>
+          <t>0,83; 1,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,9</t>
+          <t>3,52; 4,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,08</t>
+          <t>1,41; 2,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,38</t>
+          <t>0,86; 1,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 4,6</t>
+          <t>3,64; 4,66</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, otros alimentos</t>
+          <t>Población que desayuna, otros alimentos (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19039; 40709</t>
+          <t>19378; 40175</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7788; 25756</t>
+          <t>7819; 25908</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17792; 36626</t>
+          <t>17942; 36924</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21850; 42819</t>
+          <t>21690; 43271</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7306; 21784</t>
+          <t>7653; 22413</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30742; 57306</t>
+          <t>30691; 56787</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46780; 77802</t>
+          <t>46292; 77242</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18297; 43345</t>
+          <t>18981; 43395</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54396; 85063</t>
+          <t>54678; 87744</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15597; 36245</t>
+          <t>15003; 35505</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11277; 29574</t>
+          <t>11092; 28822</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67020; 102542</t>
+          <t>65898; 103937</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13329; 31396</t>
+          <t>13287; 31598</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9821; 27237</t>
+          <t>10091; 26774</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60025; 92119</t>
+          <t>56964; 91687</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33252; 59619</t>
+          <t>33038; 60997</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25079; 49865</t>
+          <t>24238; 49735</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133164; 185463</t>
+          <t>132615; 184343</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2689; 13702</t>
+          <t>2630; 13329</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>956; 8893</t>
+          <t>937; 7901</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16424; 37163</t>
+          <t>18266; 41719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>969; 8563</t>
+          <t>975; 9038</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4092; 18485</t>
+          <t>4688; 19253</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20997; 45536</t>
+          <t>20664; 43159</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5355; 19772</t>
+          <t>5179; 19134</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6001; 22090</t>
+          <t>6640; 23315</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44484; 75391</t>
+          <t>44196; 75998</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46143; 76136</t>
+          <t>46331; 77733</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24072; 50936</t>
+          <t>24543; 50512</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>115053; 164429</t>
+          <t>115908; 166439</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41555; 70627</t>
+          <t>42427; 71113</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28599; 54699</t>
+          <t>29393; 55694</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>123917; 172781</t>
+          <t>124290; 172905</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96628; 138150</t>
+          <t>93955; 138486</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59501; 96166</t>
+          <t>59932; 95883</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>253154; 317761</t>
+          <t>251454; 321853</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$otros-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36$otros-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,91</t>
+          <t>1,91; 3,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,66</t>
+          <t>0,81; 2,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,91</t>
+          <t>2,29; 4,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,3</t>
+          <t>1,59; 3,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,68</t>
+          <t>0,56; 1,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,72</t>
+          <t>3,12; 5,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,3</t>
+          <t>2,0; 3,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,88</t>
+          <t>0,79; 1,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,03</t>
+          <t>3,12; 5,0</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,1</t>
+          <t>0,91; 2,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,47</t>
+          <t>0,57; 1,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,01</t>
+          <t>3,2; 4,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,99</t>
+          <t>0,86; 2,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,53</t>
+          <t>0,58; 1,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,62</t>
+          <t>2,95; 4,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,86</t>
+          <t>0,99; 1,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,34</t>
+          <t>0,66; 1,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,54</t>
+          <t>3,29; 4,53</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,43</t>
+          <t>0,58; 2,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,37 +908,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 7,63</t>
+          <t>3,22; 7,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,9</t>
+          <t>0,2; 2,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,21</t>
+          <t>0,97; 4,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,86</t>
+          <t>3,71; 7,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,86</t>
+          <t>0,51; 1,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,49</t>
+          <t>0,73; 2,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,93</t>
+          <t>4,03; 6,89</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,38</t>
+          <t>1,36; 2,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,48</t>
+          <t>0,73; 1,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,93</t>
+          <t>3,4; 4,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,11</t>
+          <t>1,26; 2,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,57</t>
+          <t>0,79; 1,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,9</t>
+          <t>3,47; 4,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,08</t>
+          <t>1,4; 2,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,38</t>
+          <t>0,85; 1,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 4,66</t>
+          <t>3,66; 4,63</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19378; 40175</t>
+          <t>19646; 40154</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7819; 25908</t>
+          <t>7849; 26362</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17942; 36924</t>
+          <t>17260; 37476</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21690; 43271</t>
+          <t>20871; 42049</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7653; 22413</t>
+          <t>7441; 22175</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30691; 56787</t>
+          <t>30967; 56449</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46292; 77242</t>
+          <t>46753; 75626</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18981; 43395</t>
+          <t>18163; 41432</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54678; 87744</t>
+          <t>54464; 87262</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15003; 35505</t>
+          <t>15403; 36410</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11092; 28822</t>
+          <t>11174; 29517</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65898; 103937</t>
+          <t>66380; 103074</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13287; 31598</t>
+          <t>13673; 31719</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10091; 26774</t>
+          <t>10175; 26378</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56964; 91687</t>
+          <t>58643; 92250</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33038; 60997</t>
+          <t>32583; 58912</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24238; 49735</t>
+          <t>24488; 48199</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>132615; 184343</t>
+          <t>133714; 183966</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2630; 13329</t>
+          <t>3163; 14011</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>937; 7901</t>
+          <t>945; 7918</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18266; 41719</t>
+          <t>17606; 38917</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>975; 9038</t>
+          <t>971; 9539</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4688; 19253</t>
+          <t>4419; 19675</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20664; 43159</t>
+          <t>20362; 43695</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5179; 19134</t>
+          <t>5203; 18948</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6640; 23315</t>
+          <t>6808; 22715</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44196; 75998</t>
+          <t>44198; 75492</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46331; 77733</t>
+          <t>44323; 76151</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24543; 50512</t>
+          <t>24823; 50764</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>115908; 166439</t>
+          <t>114794; 163325</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42427; 71113</t>
+          <t>42586; 71838</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29393; 55694</t>
+          <t>27989; 56548</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>124290; 172905</t>
+          <t>122497; 172226</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93955; 138486</t>
+          <t>93219; 136291</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59932; 95883</t>
+          <t>59006; 94970</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>251454; 321853</t>
+          <t>252346; 319397</t>
         </is>
       </c>
     </row>
